--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26348,7 +26348,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27932,7 +27932,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28724,7 +28724,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29516,7 +29516,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30308,7 +30308,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31892,7 +31892,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33476,7 +33476,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36644,7 +36644,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37436,7 +37436,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39812,7 +39812,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40604,7 +40604,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41396,7 +41396,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42188,7 +42188,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42980,7 +42980,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43772,7 +43772,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44564,7 +44564,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45356,7 +45356,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46940,7 +46940,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47732,7 +47732,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1161,9 +1161,6 @@
       <c r="O4" t="n">
         <v>63</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>1.217108723452903</v>
       </c>
@@ -1953,9 +1950,6 @@
       <c r="O8" t="n">
         <v>196</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>3.786560472964586</v>
       </c>
@@ -2745,9 +2739,6 @@
       <c r="O12" t="n">
         <v>295</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>5.699159895533433</v>
       </c>
@@ -3537,9 +3528,6 @@
       <c r="O16" t="n">
         <v>352</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>6.800353502467012</v>
       </c>
@@ -4329,9 +4317,6 @@
       <c r="O20" t="n">
         <v>245</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>4.733200591205733</v>
       </c>
@@ -5121,9 +5106,6 @@
       <c r="O24" t="n">
         <v>134</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>2.588770935598237</v>
       </c>
@@ -5913,9 +5895,6 @@
       <c r="O28" t="n">
         <v>57</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.101193606933579</v>
       </c>
@@ -6705,9 +6684,6 @@
       <c r="O32" t="n">
         <v>19</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.3670645356445262</v>
       </c>
@@ -7497,9 +7473,6 @@
       <c r="O36" t="n">
         <v>10</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -8289,9 +8262,6 @@
       <c r="O40" t="n">
         <v>10</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -9081,9 +9051,6 @@
       <c r="O44" t="n">
         <v>17</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.3284261634714182</v>
       </c>
@@ -9873,9 +9840,6 @@
       <c r="O48" t="n">
         <v>39</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.7534482573756064</v>
       </c>
@@ -10665,9 +10629,6 @@
       <c r="O52" t="n">
         <v>69</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>1.329999724362376</v>
       </c>
@@ -11457,9 +11418,6 @@
       <c r="O56" t="n">
         <v>104</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>2.00463726570561</v>
       </c>
@@ -12249,9 +12207,6 @@
       <c r="O60" t="n">
         <v>259</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>4.992317805939932</v>
       </c>
@@ -13041,9 +12996,6 @@
       <c r="O64" t="n">
         <v>336</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>6.476520396895049</v>
       </c>
@@ -13833,9 +13785,6 @@
       <c r="O68" t="n">
         <v>266</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>5.127245314208579</v>
       </c>
@@ -14625,9 +14574,6 @@
       <c r="O72" t="n">
         <v>172</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>3.315361631743894</v>
       </c>
@@ -15417,9 +15363,6 @@
       <c r="O76" t="n">
         <v>72</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.387825799334653</v>
       </c>
@@ -16209,9 +16152,6 @@
       <c r="O80" t="n">
         <v>13</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.2505796582132013</v>
       </c>
@@ -17001,9 +16941,6 @@
       <c r="O84" t="n">
         <v>16</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.3084057331854785</v>
       </c>
@@ -17793,9 +17730,6 @@
       <c r="O88" t="n">
         <v>20</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.3855071664818481</v>
       </c>
@@ -18585,9 +18519,6 @@
       <c r="O92" t="n">
         <v>9</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.1734782249168317</v>
       </c>
@@ -19377,9 +19308,6 @@
       <c r="O96" t="n">
         <v>59</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>1.137246141121452</v>
       </c>
@@ -20169,9 +20097,6 @@
       <c r="O100" t="n">
         <v>130</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>2.499737527559606</v>
       </c>
@@ -20961,9 +20886,6 @@
       <c r="O104" t="n">
         <v>192</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>3.691920040703419</v>
       </c>
@@ -21753,9 +21675,6 @@
       <c r="O108" t="n">
         <v>247</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>4.749501302363252</v>
       </c>
@@ -22545,9 +22464,6 @@
       <c r="O112" t="n">
         <v>308</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>5.922455065295067</v>
       </c>
@@ -23337,9 +23253,6 @@
       <c r="O116" t="n">
         <v>229</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>4.403383798547306</v>
       </c>
@@ -24129,9 +24042,6 @@
       <c r="O120" t="n">
         <v>167</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>3.211201285403494</v>
       </c>
@@ -24921,9 +24831,6 @@
       <c r="O124" t="n">
         <v>45</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.8652937595398636</v>
       </c>
@@ -25713,9 +25620,6 @@
       <c r="O128" t="n">
         <v>16</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.3076600033919515</v>
       </c>
@@ -26505,9 +26409,6 @@
       <c r="O132" t="n">
         <v>14</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.2692025029679576</v>
       </c>
@@ -27297,9 +27198,6 @@
       <c r="O136" t="n">
         <v>29</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.5576337561479121</v>
       </c>
@@ -28089,9 +27987,6 @@
       <c r="O140" t="n">
         <v>54</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>1.038352511447836</v>
       </c>
@@ -28881,9 +28776,6 @@
       <c r="O144" t="n">
         <v>119</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>2.28822127522764</v>
       </c>
@@ -29673,9 +29565,6 @@
       <c r="O148" t="n">
         <v>229</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>4.392901914557099</v>
       </c>
@@ -30465,9 +30354,6 @@
       <c r="O152" t="n">
         <v>335</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>6.426297560596629</v>
       </c>
@@ -31257,9 +31143,6 @@
       <c r="O156" t="n">
         <v>475</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>9.111914451592234</v>
       </c>
@@ -32049,9 +31932,6 @@
       <c r="O160" t="n">
         <v>465</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>8.920084673663977</v>
       </c>
@@ -32841,9 +32721,6 @@
       <c r="O164" t="n">
         <v>317</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>6.081003960325766</v>
       </c>
@@ -33633,9 +33510,6 @@
       <c r="O168" t="n">
         <v>131</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>2.512970090860174</v>
       </c>
@@ -34425,9 +34299,6 @@
       <c r="O172" t="n">
         <v>59</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.13179568977672</v>
       </c>
@@ -35217,9 +35088,6 @@
       <c r="O176" t="n">
         <v>17</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.3261106224780379</v>
       </c>
@@ -36009,9 +35877,6 @@
       <c r="O180" t="n">
         <v>18</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.3452936002708636</v>
       </c>
@@ -36801,9 +36666,6 @@
       <c r="O184" t="n">
         <v>19</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.3644765780636894</v>
       </c>
@@ -37593,9 +37455,6 @@
       <c r="O188" t="n">
         <v>59</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>1.13179568977672</v>
       </c>
@@ -38385,9 +38244,6 @@
       <c r="O192" t="n">
         <v>61</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>1.170161645362371</v>
       </c>
@@ -39177,9 +39033,6 @@
       <c r="O196" t="n">
         <v>128</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>2.448285702700077</v>
       </c>
@@ -39969,9 +39822,6 @@
       <c r="O200" t="n">
         <v>232</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>4.437517836143889</v>
       </c>
@@ -40761,9 +40611,6 @@
       <c r="O204" t="n">
         <v>221</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>4.227118283568101</v>
       </c>
@@ -41553,9 +41400,6 @@
       <c r="O208" t="n">
         <v>222</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>4.246245515620446</v>
       </c>
@@ -42345,9 +42189,6 @@
       <c r="O212" t="n">
         <v>191</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>3.653301321997771</v>
       </c>
@@ -43137,9 +42978,6 @@
       <c r="O216" t="n">
         <v>143</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>2.735194183485242</v>
       </c>
@@ -43929,9 +43767,6 @@
       <c r="O220" t="n">
         <v>71</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>1.358033475716449</v>
       </c>
@@ -44721,9 +44556,6 @@
       <c r="O224" t="n">
         <v>22</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.4207991051515756</v>
       </c>
@@ -45513,9 +45345,6 @@
       <c r="O228" t="n">
         <v>11</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.2103995525757878</v>
       </c>
@@ -46305,9 +46134,6 @@
       <c r="O232" t="n">
         <v>12</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.2295267846281322</v>
       </c>
@@ -47097,9 +46923,6 @@
       <c r="O236" t="n">
         <v>20</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.382544641046887</v>
       </c>
@@ -47888,9 +47711,6 @@
       </c>
       <c r="O240" t="n">
         <v>52</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0.9946160667219061</v>

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22317,7 +22317,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29418,7 +29418,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30207,7 +30207,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35730,7 +35730,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38097,7 +38097,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40464,7 +40464,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41253,7 +41253,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42042,7 +42042,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -42831,7 +42831,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45198,7 +45198,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46776,7 +46776,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47565,7 +47565,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39665,7 +39665,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44399,7 +44399,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46766,7 +46766,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39665,7 +39665,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44399,7 +44399,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46766,7 +46766,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39665,7 +39665,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44399,7 +44399,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46766,7 +46766,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">

--- a/diseases/d199/2000-2004.xlsx
+++ b/diseases/d199/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39665,7 +39665,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42032,7 +42032,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43610,7 +43610,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44399,7 +44399,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45188,7 +45188,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46766,7 +46766,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
